--- a/docs/Master-Data-Akun-Instruktur-DailyDose.xlsx
+++ b/docs/Master-Data-Akun-Instruktur-DailyDose.xlsx
@@ -1295,7 +1295,7 @@
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>bc7bd5a8-078a-4aec-867b-c73e4d38a6d8</t>
+          <t>52e477aa-71f5-4560-95d0-a43128ff3b98</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>bfb3053f-401b-4518-9a06-5c1c696667a6</t>
+          <t>68fadaea-1755-488f-b97e-9dc68fe6a102</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>034924c9-c318-41a8-8316-690eb054954c</t>
+          <t>9a2a800b-c1b3-46b6-9a2a-8fe8e64b8f03</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>

--- a/docs/Master-Data-Akun-Instruktur-DailyDose.xlsx
+++ b/docs/Master-Data-Akun-Instruktur-DailyDose.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -636,7 +636,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -1896,6 +1895,66 @@
       <c r="L25" s="14" t="inlineStr">
         <is>
           <t>9a2a800b-c1b3-46b6-9a2a-8fe8e64b8f03</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kezia</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Kezia</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>UNTAR</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>keziaUNTAR</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SUKSES (200)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>kezia.untar@dailydosepilates.com</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2bd5b036-b141-4154-abac-2af744c2f952</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -3108,6 +3167,46 @@
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>SUKSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Kezia</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>UNTAR</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>keziaUNTAR</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>SUKSES</t>
         </is>
@@ -3158,7 +3257,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>

--- a/docs/Master-Data-Akun-Instruktur-DailyDose.xlsx
+++ b/docs/Master-Data-Akun-Instruktur-DailyDose.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>afifahGG</t>
+          <t>afifah</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>annaGGMK</t>
+          <t>annadesi</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>asriGGMK</t>
+          <t>asrigelv</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>devi_GG</t>
+          <t>deviocta</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>fendy</t>
+          <t>fendyher</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>gressyaMK</t>
+          <t>gressya</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>indahUNTAR</t>
+          <t>indahper</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>lailyGGPIK</t>
+          <t>lailysor</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>linaMKUNTAR</t>
+          <t>linalind</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>listyUNTAR</t>
+          <t>listya</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>luciaGG</t>
+          <t>luciacha</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>naokkiUNTAR</t>
+          <t>naokki</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>oliviaGGPIK</t>
+          <t>oliviana</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>silvester</t>
+          <t>silvest</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>stefannyPIK2</t>
+          <t>stefanny</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>susanPIK</t>
+          <t>susanwid</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>vaniaUNTAR</t>
+          <t>vaniah</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>vinnyUNTAR</t>
+          <t>vinnyy</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>violaGG</t>
+          <t>violand</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>violettaPIK</t>
+          <t>violetta</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>keziaUNTAR</t>
+          <t>keziaa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Green Garden (10) · Muara Karang (5) · Orange Groves PIK 2 (5) · Untar Kampus 2 (7)</t>
+          <t>Green Garden (10) · Muara Karang (5) · Orange Groves PIK 2 (5) · Untar Kampus 2 (8)</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>afifahGG</t>
+          <t>afifah</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>annaGGMK</t>
+          <t>annadesi</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>asriGGMK</t>
+          <t>asrigelv</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>devi_GG</t>
+          <t>deviocta</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>fendy</t>
+          <t>fendyher</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lailyGGPIK</t>
+          <t>lailysor</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>luciaGG</t>
+          <t>luciacha</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>oliviaGGPIK</t>
+          <t>oliviana</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>silvester</t>
+          <t>silvest</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>violaGG</t>
+          <t>violand</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>annaGGMK</t>
+          <t>annadesi</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>asriGGMK</t>
+          <t>asrigelv</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>gressyaMK</t>
+          <t>gressya</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>linaMKUNTAR</t>
+          <t>linalind</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>silvester</t>
+          <t>silvest</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>lailyGGPIK</t>
+          <t>lailysor</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>oliviaGGPIK</t>
+          <t>oliviana</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>stefannyPIK2</t>
+          <t>stefanny</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>susanPIK</t>
+          <t>susanwid</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>violettaPIK</t>
+          <t>violetta</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>fendy</t>
+          <t>fendyher</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>indahUNTAR</t>
+          <t>indahper</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>linaMKUNTAR</t>
+          <t>linalind</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>listyUNTAR</t>
+          <t>listya</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>naokkiUNTAR</t>
+          <t>naokki</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>vaniaUNTAR</t>
+          <t>vaniah</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>vinnyUNTAR</t>
+          <t>vinnyy</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>keziaUNTAR</t>
+          <t>keziaa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
